--- a/artfynd/A 5701-2023 artfynd.xlsx
+++ b/artfynd/A 5701-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5701-2023 artfynd.xlsx
+++ b/artfynd/A 5701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66969050</v>
+        <v>66969052</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>388</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633740.0633843344</v>
+        <v>633638</v>
       </c>
       <c r="R2" t="n">
-        <v>7117665.036573363</v>
+        <v>7117796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66969046</v>
+        <v>111519523</v>
       </c>
       <c r="B3" t="n">
-        <v>5426</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,43 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101410</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baksjönäs väst, Ås lm</t>
+          <t>Baksjönäs, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633789.95866321</v>
+        <v>633715</v>
       </c>
       <c r="R3" t="n">
-        <v>7117644.042597923</v>
+        <v>7117627</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,27 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66969051</v>
+        <v>66969050</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,39 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Baksjönäs väst, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633736.950844523</v>
+        <v>633740</v>
       </c>
       <c r="R4" t="n">
-        <v>7117666.212464367</v>
+        <v>7117665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +941,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66969052</v>
+        <v>66969049</v>
       </c>
       <c r="B5" t="n">
-        <v>78472</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>388</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633638.1779964247</v>
+        <v>633740</v>
       </c>
       <c r="R5" t="n">
-        <v>7117796.04548391</v>
+        <v>7117665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,19 +1038,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,50 +1067,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66969048</v>
+        <v>111519525</v>
       </c>
       <c r="B6" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjönäs väst, Ås lm</t>
+          <t>Baksjönäs, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633748.0695372439</v>
+        <v>633449</v>
       </c>
       <c r="R6" t="n">
-        <v>7117651.841144198</v>
+        <v>7117893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,22 +1132,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,49 +1152,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66969049</v>
+        <v>66969047</v>
       </c>
       <c r="B7" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633740.0633843344</v>
+        <v>633748</v>
       </c>
       <c r="R7" t="n">
-        <v>7117665.036573363</v>
+        <v>7117652</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,19 +1236,9 @@
           <t>2017-06-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,50 +1265,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66969047</v>
+        <v>111519524</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Baksjönäs väst, Ås lm</t>
+          <t>Baksjönäs, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633748.0695372439</v>
+        <v>633584</v>
       </c>
       <c r="R8" t="n">
-        <v>7117651.841144198</v>
+        <v>7117851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,22 +1330,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-06-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,27 +1350,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111519525</v>
+        <v>1979685</v>
       </c>
       <c r="B9" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,34 +1377,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjönäs, Ås lm</t>
+          <t>Borgsjö, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633449.4009562896</v>
+        <v>633784</v>
       </c>
       <c r="R9" t="n">
-        <v>7117893.599162375</v>
+        <v>7117669</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1543,22 +1431,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-07-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1569,70 +1447,74 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>tallskog</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>1 substratenheter # brandstubbe av tall</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111519524</v>
+        <v>66969048</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjönäs, Ås lm</t>
+          <t>Baksjönäs väst, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633583.7615760232</v>
+        <v>633748</v>
       </c>
       <c r="R10" t="n">
-        <v>7117850.915647855</v>
+        <v>7117652</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,22 +1541,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,31 +1561,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111519523</v>
+        <v>66969051</v>
       </c>
       <c r="B11" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1721,34 +1584,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Baksjönäs, Ås lm</t>
+          <t>Baksjönäs väst, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633714.5983269843</v>
+        <v>633737</v>
       </c>
       <c r="R11" t="n">
-        <v>7117626.805168894</v>
+        <v>7117666</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,22 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,19 +1663,121 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>66969046</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5495</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Baksjönäs väst, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>633790</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7117644</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-06-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5701-2023 artfynd.xlsx
+++ b/artfynd/A 5701-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969052</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111519523</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1165,6 +1190,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111519525</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1262,6 +1292,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111519524</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1979685</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1778,8 +1833,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66969046</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>